--- a/source_data/Figure1.xlsx
+++ b/source_data/Figure1.xlsx
@@ -5,17 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weikangshi/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weikangshi/Desktop/PostDoc/manuscripts_move_to_dropbox/gaze_accumulation_marmoset_dmPFC/final_after_rebuttal/source_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{144DA8A5-72E6-904B-AF30-4E6141D76A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EF55A4-852C-EA4C-8366-F83ABE3E7239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="5480" windowWidth="28040" windowHeight="17180" xr2:uid="{CDD6E5A6-FA5B-EC4D-9D0B-223207B8A016}"/>
+    <workbookView xWindow="18180" yWindow="2420" windowWidth="28040" windowHeight="17180" activeTab="4" xr2:uid="{CDD6E5A6-FA5B-EC4D-9D0B-223207B8A016}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="panelC" sheetId="1" r:id="rId1"/>
+    <sheet name="panelD" sheetId="2" r:id="rId2"/>
+    <sheet name="panelE" sheetId="4" r:id="rId3"/>
+    <sheet name="panelF" sheetId="5" r:id="rId4"/>
+    <sheet name="panelH" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,15 +39,53 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+  <si>
+    <t>coefficient value</t>
+  </si>
+  <si>
+    <t>animal K</t>
+  </si>
+  <si>
+    <t>beta 1</t>
+  </si>
+  <si>
+    <t>beta 2</t>
+  </si>
+  <si>
+    <t>beta 3</t>
+  </si>
+  <si>
+    <t>beta 4</t>
+  </si>
+  <si>
+    <t>animal D</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,8 +108,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -407,4 +454,730 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801AA4C3-78C4-0644-86A1-B6B1DB98E3B4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A123C4A-92D5-544D-90FE-40151423B72C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E754120-16BB-9F43-BAE4-B6EF8B27035B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE5060A-0E39-AF4B-8A3E-E2FF4D0897F5}">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="11" max="14" width="18.6640625" customWidth="1"/>
+    <col min="15" max="19" width="31.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>0.82087500000000002</v>
+      </c>
+      <c r="B4" s="3">
+        <v>-0.21607799999999999</v>
+      </c>
+      <c r="C4" s="3">
+        <v>-6.5360000000000001E-2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>-0.180232</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.9932430000000001</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-5.1581000000000002E-2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>5.9309000000000001E-2</v>
+      </c>
+      <c r="H4" s="3">
+        <v>8.6544999999999997E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>0.52890000000000004</v>
+      </c>
+      <c r="B5" s="3">
+        <v>-0.19245699999999999</v>
+      </c>
+      <c r="C5" s="3">
+        <v>-0.10753500000000001</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-0.19172900000000001</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.57758799999999999</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-0.83158200000000004</v>
+      </c>
+      <c r="G5" s="3">
+        <v>-4.7809999999999998E-2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-2.6787999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>1.450642</v>
+      </c>
+      <c r="B6" s="3">
+        <v>-0.28647499999999998</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.109831</v>
+      </c>
+      <c r="D6" s="3">
+        <v>-3.3495999999999998E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.9811830000000001</v>
+      </c>
+      <c r="F6" s="3">
+        <v>-1.041728</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.16528100000000001</v>
+      </c>
+      <c r="H6" s="3">
+        <v>-1.7779E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>0.37209100000000001</v>
+      </c>
+      <c r="B7" s="3">
+        <v>-0.53828699999999996</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.180085</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.12027500000000001</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.37015900000000002</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.64276</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.19134300000000001</v>
+      </c>
+      <c r="H7" s="3">
+        <v>-0.28320200000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>0.92419799999999996</v>
+      </c>
+      <c r="B8" s="3">
+        <v>-0.64675899999999997</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-0.14435500000000001</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-0.173786</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.902031</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.47867199999999999</v>
+      </c>
+      <c r="G8" s="3">
+        <v>-2.5429E-2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>-3.0853999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>0.89568099999999995</v>
+      </c>
+      <c r="B9" s="3">
+        <v>-0.174147</v>
+      </c>
+      <c r="C9" s="3">
+        <v>-0.15351100000000001</v>
+      </c>
+      <c r="D9" s="3">
+        <v>-1.4651000000000001E-2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.9359999999999999</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-0.89007000000000003</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.25706400000000001</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-0.100953</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>0.68008800000000003</v>
+      </c>
+      <c r="B10" s="3">
+        <v>-1.176329</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.134935</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-0.35796600000000001</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.07141</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-0.51232200000000006</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-0.39761000000000002</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3.7819999999999999E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>0.22783900000000001</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-1.151667</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1.8633E-2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>-0.145202</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.47490100000000002</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.54366499999999995</v>
+      </c>
+      <c r="G11" s="3">
+        <v>-6.7030000000000006E-2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>-6.4474000000000004E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>0.621421</v>
+      </c>
+      <c r="B12" s="3">
+        <v>-0.43262099999999998</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-1.2148000000000001E-2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-0.174425</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.73766699999999996</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7.9117999999999994E-2</v>
+      </c>
+      <c r="G12" s="3">
+        <v>-3.2018999999999999E-2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.147504</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>1.0601849999999999</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.94842099999999996</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.75722900000000004</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-0.67113400000000001</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.73829500000000003</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-3.4084999999999997E-2</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1.502864</v>
+      </c>
+      <c r="H13" s="3">
+        <v>-0.30751000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>0.42945699999999998</v>
+      </c>
+      <c r="B14" s="3">
+        <v>-0.133349</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.44294600000000001</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-4.7292000000000001E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.268874</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-0.25893500000000003</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-8.4960999999999995E-2</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-7.6425999999999994E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>0.79688000000000003</v>
+      </c>
+      <c r="B15" s="3">
+        <v>-0.76157799999999998</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.99036299999999999</v>
+      </c>
+      <c r="D15" s="3">
+        <v>-1.4060049999999999</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.020786</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-0.29178599999999999</v>
+      </c>
+      <c r="G15" s="3">
+        <v>-0.21916099999999999</v>
+      </c>
+      <c r="H15" s="3">
+        <v>5.4656999999999997E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>0.66328399999999998</v>
+      </c>
+      <c r="B16" s="3">
+        <v>-9.2586000000000002E-2</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-0.40767700000000001</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.16594400000000001</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.44327899999999998</v>
+      </c>
+      <c r="F16" s="3">
+        <v>-0.65977600000000003</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.31325900000000001</v>
+      </c>
+      <c r="H16" s="3">
+        <v>-0.214392</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>0.52407199999999998</v>
+      </c>
+      <c r="B17" s="3">
+        <v>-0.28096500000000002</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-1.3854E-2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>-0.18654299999999999</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9.6069000000000002E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.131329</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.40843699999999999</v>
+      </c>
+      <c r="H17" s="3">
+        <v>-8.5356000000000001E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>0.53908900000000004</v>
+      </c>
+      <c r="B18" s="3">
+        <v>-0.31161499999999998</v>
+      </c>
+      <c r="C18" s="3">
+        <v>-1.0995E-2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.11010300000000001</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.32159399999999999</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-0.78598000000000001</v>
+      </c>
+      <c r="G18" s="3">
+        <v>6.1251E-2</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.336E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>0.69115300000000002</v>
+      </c>
+      <c r="B19" s="3">
+        <v>-0.25150400000000001</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.124538</v>
+      </c>
+      <c r="D19" s="3">
+        <v>-7.1904999999999997E-2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.93754899999999997</v>
+      </c>
+      <c r="F19" s="3">
+        <v>-0.447216</v>
+      </c>
+      <c r="G19" s="3">
+        <v>-4.0665E-2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>-0.248782</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>1.0183500000000001</v>
+      </c>
+      <c r="B20" s="3">
+        <v>-0.41274899999999998</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.121547</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.0229E-2</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2.0074510000000001</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-0.78851099999999996</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-3.1806000000000001E-2</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-5.0027000000000002E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>0.59257800000000005</v>
+      </c>
+      <c r="B21" s="3">
+        <v>6.2801999999999997E-2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.19609499999999999</v>
+      </c>
+      <c r="D21" s="3">
+        <v>-0.13441600000000001</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1.078281</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-0.181726</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-0.109038</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2.6870000000000002E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>1.4212340000000001</v>
+      </c>
+      <c r="B22" s="3">
+        <v>-5.6181000000000002E-2</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.53720400000000001</v>
+      </c>
+      <c r="D22" s="3">
+        <v>-0.37415700000000002</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2.0415100000000002</v>
+      </c>
+      <c r="F22" s="3">
+        <v>-7.9551999999999998E-2</v>
+      </c>
+      <c r="G22" s="3">
+        <v>-0.32580399999999998</v>
+      </c>
+      <c r="H22" s="3">
+        <v>-6.0026999999999997E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>0.92073700000000003</v>
+      </c>
+      <c r="B23" s="3">
+        <v>9.8242999999999997E-2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1.0617399999999999</v>
+      </c>
+      <c r="D23" s="3">
+        <v>-0.68886800000000004</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1.3493919999999999</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-0.70769000000000004</v>
+      </c>
+      <c r="G23" s="3">
+        <v>6.9253999999999996E-2</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-3.0120000000000001E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="3">
+        <v>1.1895089999999999</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.37872699999999998</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-0.177814</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-7.5401999999999997E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3">
+        <v>1.2327060000000001</v>
+      </c>
+      <c r="F25" s="3">
+        <v>-0.43092200000000003</v>
+      </c>
+      <c r="G25" s="3">
+        <v>-3.2209000000000002E-2</v>
+      </c>
+      <c r="H25" s="3">
+        <v>9.1059999999999995E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="3">
+        <v>0.71275699999999997</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-0.237236</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-5.4404000000000001E-2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-3.8061999999999999E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="3">
+        <v>4.2046419999999998</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-0.379328</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-0.52438099999999999</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-0.42396099999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="3">
+        <v>2.2732190000000001</v>
+      </c>
+      <c r="F28" s="3">
+        <v>-0.22483800000000001</v>
+      </c>
+      <c r="G28" s="3">
+        <v>-5.5404000000000002E-2</v>
+      </c>
+      <c r="H28" s="3">
+        <v>-0.15423200000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="3">
+        <v>1.4228959999999999</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0.30669999999999997</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-0.114719</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-5.3343000000000002E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>